--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H277"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-07-07 11:54:20</t>
+          <t>2026-07-07 14:46:15</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026-07-07 10:22:23</t>
+          <t>2026-07-07 14:18:39</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026-07-07 10:30:38</t>
+          <t>2026-07-07 13:58:09</t>
         </is>
       </c>
     </row>
@@ -11847,6 +11847,1686 @@
       <c r="H277" t="inlineStr">
         <is>
           <t>2026-07-07 10:40:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>AED 9.79</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/garlic-ginger/garlic-kg-ep/p/499952?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:05:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Mother's Recipe Ginger Garlic Paste 300 g</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AED 28.83/kg</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/mothers-recipe-ginger-garlic-paste-300-g/p/326600/?</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:16:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:05:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Loose Garlic</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>AED 9.75/kg</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/garlic-loose-china-462760.html</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Carrefour Fresh Cucumbers 500g</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>AED 5.58</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/cucumber/mf-fresh-cucumber-500g/p/1876556?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:26:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Snack Cucumber 250 g</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>AED 18.00/kg</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/snack-cucumber-250-g/p/1808042/?</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:27:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:27:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Snack Cucumbers</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>AED 14.00/kg</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/cucumbers/veggitech-snack-cucumbers-cucmiaexx2xxl1</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:27:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Loose Cucumber</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/cucumber-loose-uae-463632.html</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:28:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>AED 3.89</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/potato/potato-ep/p/1552234?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:04:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Potato 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>AED 4.50/kg</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/potato-2-5-kg/p/991526/?</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:56:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Potato Syria</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AED 4.24/kg</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/potato-1700602554-mdawmdawmtm4mziwmq-mdawmdawmtm4mziwmv8xnzawnjayntu0.html</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:57:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>AED 3.89</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/onion-shalots/onion-red-ep/p/447550?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Red Onion Sliced 250 g</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>AED 16.00/kg</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/red-onion-sliced-250-g/p/893372/?</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:31:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Red Onions</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>AED 6.40/kg</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/onions/kibsons-red-onions-onireinxxkgss1</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:32:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Vegan Organic Red Onion</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>AED 42.00/kg</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/red-onion-organic-1701293480-mdawmdawmtm4ndgyng-mdawmdawmtm4ndgynl8xnzaxmjkzndgw.html</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:32:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>AED 5.59</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/tomato/tomato-ep/p/1767482?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Safa Tomato Paste 850 g</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>AED 7.88/kg</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/safa-tomato-paste-850-g/p/73522/?</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:41:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Cherry Tomatoes</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>AED 28.33/kg</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/tomatoes/veggitech-cherry-tomatoes-tomcraexxxxxl1</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:41:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Plum Roma Tomato</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>AED 14.95/kg</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/ph-tomato-plum-roma-1694122664-mdk1ndg-mdk1ndhfmty5ndeymjy2na.html</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Carrefour Valencia Oranges 3Kg</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>AED 4.33</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/crf-orange-valencia-3kg/p/2175463?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:29:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Orange Valencia Egypt 1 kg</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>AED 5.65/kg</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/18993-ea/?convtobuom=1000</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:32:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Valencia Oranges</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>AED 15.00/kg</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>LEBANON</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-valencia-oranges-oravalbxxpacb1</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:36:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Valencia Orange</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>AED 4.98/kg</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-val-1706650526-mdawmdawmtm5odgzma-mdawmdawmtm5odgzmf8xnza2njuwnti2.html</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:37:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>AED 4.89</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/orange-valencia/p/446565?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Orange Navel Net Bag 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>AED 8.78/kg</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/orange-navel-net-bag-2-5-kg/p/736733/?</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:29:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Watermelon Dark</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>AED 5.39</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/melon/watermelon-dark/p/446215?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:20:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Sweet Potatoes</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>AED 21.95/kg</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/potatoes/kibsons-sweet-potatoes-potxxusxxkgsa1</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>2026-07-08 12:57:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Purple Garlic</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>AED 86.76/kg</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>SPAIN</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/garlic-ginger/kibsons-purple-garlic-garpuesxx30ps1</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:08:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Watermelon Saudi 2 kg</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>AED 4.45/kg</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/watermelon-saudi-2-kg/p/2262476-ea/?convtobuom=2000</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:20:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:22:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Navel Oranges</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>AED 9.29/kg</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>SOUTH AFRICA</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-navel-oranges-oranazakbctns1</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:23:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Watermelon Kernel</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>AED 65.00/kg</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>NATURE'S CHOICE</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/pantry/nuts-seeds-dried-fruits/natures-choice-watermelon-kernel-fxswaaenc100l1</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Navel Orange South Africa</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>AED 10.50/kg</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-navel-1700602551-mdawmdawmtm4mza0mq-mdawmdawmtm4mza0mv8xnzawnjayntux.html</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:24:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/water-melon-1756071158-mde3mja-mde3mjbfmtc1nja3mte1oa.html</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:25:19</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2026-07-08 13:19:15</t>
+          <t>2026-07-08 16:10:50</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Red Onion Sliced 250 g</t>
+          <t>Vatika Naturals Red Onion Hair Fall Shampoo 2 x 400 ml</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>AED 16.00/kg</t>
+          <t>AED 33.31/L</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>https://gcc.luluhypermarket.com/en-ae/red-onion-sliced-250-g/p/893372/?</t>
+          <t>https://gcc.luluhypermarket.com/en-ae/vatika-naturals-red-onion-hair-fall-shampoo-2-x-400-ml/p/2446337/?</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026-07-08 12:31:31</t>
+          <t>2026-07-08 16:11:02</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AED 85.68/kg</t>
+          <t>AED 12.95/kg</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-07-08 12:31:56</t>
+          <t>2026-07-08 16:11:14</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026-07-08 12:32:22</t>
+          <t>2026-07-08 16:11:32</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-07-08 12:32:35</t>
+          <t>2026-07-08 16:11:44</t>
         </is>
       </c>
     </row>
@@ -13527,6 +13527,2232 @@
       <c r="H317" t="inlineStr">
         <is>
           <t>2026-07-08 13:25:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>AED 9.79</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/garlic-ginger/garlic-kg-ep/p/499952?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:20:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Shan Ginger Garlic Paste 310 g</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>AED 30.81/kg</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/shan-ginger-garlic-paste-310-g/p/652365/?</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:20:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:20:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Loose Garlic</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>AED 9.75/kg</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/garlic-loose-china-462760.html</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:21:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Purple Garlic</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>AED 86.76/kg</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>SPAIN</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/garlic-ginger/kibsons-purple-garlic-garpuesxx30ps1</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Carrefour Fresh Cucumbers 500g</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>AED 5.58</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/cucumber/mf-fresh-cucumber-500g/p/1876556?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Snack Cucumber 250 g</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>AED 18.00/kg</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/snack-cucumber-250-g/p/1808042/?</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:23:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:23:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Loose Cucumber</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/cucumber-loose-uae-463632.html</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Snack Cucumbers</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>AED 14.00/kg</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/cucumbers/veggitech-snack-cucumbers-cucmiaexx2xxl1</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:24:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>AED 3.89</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/potato/potato-ep/p/1552234?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:25:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Potato 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>AED 4.50/kg</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/potato-2-5-kg/p/991526/?</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:25:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:25:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Sweet Potatoes</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>AED 21.95/kg</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/potatoes/kibsons-sweet-potatoes-potxxusxxkgsa1</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:26:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Loose Potato</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>AED 3.65/kg</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/potato-loose-washed-egypt-463229.html</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:26:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>AED 3.89</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/onion-shalots/onion-red-ep/p/447550?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Onion Bag 2 kg</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>AED 4.47/kg</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/onion-bag-2-kg/p/797576/?</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:27:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:27:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Red Onions</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>AED 6.40/kg</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/onions/kibsons-red-onions-onireinxxkgss1</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:27:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Vegan Organic Red Onion</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>AED 42.00/kg</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/red-onion-organic-1701293480-mdawmdawmtm4ndgyng-mdawmdawmtm4ndgynl8xnzaxmjkzndgw.html</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:28:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Pure Harvest Candy Tomatoes 350g</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>AED 25.69</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/tomato/tomato-candy-350g-ph/p/1576307?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:28:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Tomato Bunch 500 g</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>AED 10.96/kg</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/tomato-bunch-500-g/p/812197-ea/?convtobuom=500</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:28:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:29:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Cherry Tomatoes</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>AED 28.33/kg</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/tomatoes/veggitech-cherry-tomatoes-tomcraexxxxxl1</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:29:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>AED 5.50/kg</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/tomato-per-kg-4409651.html</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:31:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>AED 4.89</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/orange-valencia/p/446565?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Orange Valencia Egypt 1 kg</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>AED 5.65/kg</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/18993-ea/?convtobuom=1000</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:23:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>AED 8.49</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/orange-navel/p/71069?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:14:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Orange Navel Net Bag 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>AED 8.78/kg</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/orange-navel-net-bag-2-5-kg/p/736733/?</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:14:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:14:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Navel Oranges</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>AED 9.29/kg</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>SOUTH AFRICA</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-navel-oranges-oranazakbctns1</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>South Africa Orange Naval Cambria</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>AED 8.95/kg</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-naval-cambria-1755379961-mdywnze-mdywnzffmtc1ntm3otk2mq.html</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>2026-07-09 17:08:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Valencia Oranges</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>AED 15.00/kg</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>LEBANON</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-valencia-oranges-oravalbxxpacb1</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:20:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Orange Organic</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>AED 51.90/kg</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-organic-1695423680-odk1njiznzc4otu2nq-odk1njiznzc4otu2nv8xnjk1ndiznjgw.html</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>2026-07-09 17:10:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Watermelon Dark</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>AED 5.39</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/melon/watermelon-dark/p/446215?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:24:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Watermelon Jordan 3 kg</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/watermelon-jordan-3-kg/p/535969-ea/?convtobuom=3000</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:24:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Fit Fresh Watermelon Cubes</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>AED 34.00/kg</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/fresh-watermelon-cubes-250gm-1647293847-nji5mtewnjg0mta5mq.html</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:25:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Watermelon Kernel</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>AED 65.00/kg</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>NATURE'S CHOICE</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/pantry/nuts-seeds-dried-fruits/natures-choice-watermelon-kernel-fxswaaenc100l1</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:25:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>AED 9.69</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/garlic-ginger/garlic-kg-ep/p/499952?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:23:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Shan Ginger Garlic Paste 310 g</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>AED 30.81/kg</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/shan-ginger-garlic-paste-310-g/p/652365/?</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:23:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:23:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Loose Garlic</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>AED 9.75/kg</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/garlic-loose-china-462760.html</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Purple Garlic</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>AED 86.76/kg</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>SPAIN</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/garlic-ginger/kibsons-purple-garlic-garpuesxx30ps1</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:25:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Carrefour Fresh Cucumbers 500g</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>AED 5.58</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/cucumber/mf-fresh-cucumber-500g/p/1876556?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:27:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Cucumber 500 g</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>AED 5.96/kg</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/18574-ea/?convtobuom=500</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:28:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:28:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Loose Cucumber</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/cucumber-loose-uae-463632.html</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:28:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Snack Cucumbers</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>AED 14.00/kg</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/cucumbers/veggitech-snack-cucumbers-cucmiaexx2xxl1</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:29:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Sweet Potato (Orange)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>AED 9.99</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/potato/potato-sweet-import/p/458471?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:30:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Potato UAE 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>AED 3.58/kg</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/potato-uae-25-kg/p/1484373/?</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:30:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:31:19</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H370"/>
+  <dimension ref="A1:H397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>2026-07-10 12:23:05</t>
+          <t>2026-07-10 13:47:41</t>
         </is>
       </c>
     </row>
@@ -15753,6 +15753,1140 @@
       <c r="H370" t="inlineStr">
         <is>
           <t>2026-07-10 12:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Sweet Potatoes</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>AED 21.95/kg</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/potatoes/kibsons-sweet-potatoes-potxxusxxkgsa1</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Potato Syria</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>AED 4.24/kg</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/potato-1700602554-mdawmdawmtm4mziwmq-mdawmdawmtm4mziwmv8xnzawnjayntu0.html</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:31:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>AED 3.79</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/onion-shalots/onion-red-ep/p/447550?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:32:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Red Apple USA 1 kg</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>AED 14.95/kg</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/red-apple-usa-1-kg/p/19047-ea/?convtobuom=1000</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:32:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Red Onions</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>AED 6.40/kg</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/onions/kibsons-red-onions-onireinxxkgss1</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:33:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Vegan Organic Red Onion</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>AED 42.00/kg</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/red-onion-organic-1701293480-mdawmdawmtm4ndgyng-mdawmdawmtm4ndgynl8xnzaxmjkzndgw.html</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:33:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Premium Tomato Bunch</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>AED 11.99</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/tomato/tomato-bunch-red-premium-ph/p/1792194?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:34:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Tomato Jordan 500 g</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>AED 5.96/kg</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/372444-ea/?convtobuom=500</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:34:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>AED 5.50/kg</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/tomato-per-kg-4409651.html</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:35:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Cherry Plum Tomatoes</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>AED 24.00/kg</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/tomatoes/veggitech-cherry-plum-tomatoes-checpaevgxxxl1</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>AED 10.29</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/di-orange-valencia-leb/p/2243049?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>2026-07-10 13:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Orange Valencia 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>AED 5.98/kg</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/orange-valencia-2-5-kg/p/736734/?</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:39:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:39:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Valencia Oranges</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>AED 15.00/kg</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>LEBANON</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-valencia-oranges-oravalbxxpacb1</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:40:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Orange Organic</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>AED 51.90/kg</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-organic-1695423680-odk1njiznzc4otu2nq-odk1njiznzc4otu2nv8xnjk1ndiznjgw.html</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:40:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>AED 8.89</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/orange-navel/p/71069?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:46:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Orange Navel Net Bag 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>AED 8.78/kg</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/orange-navel-net-bag-2-5-kg/p/736733/?</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:46:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:47:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Navel Oranges</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>AED 9.29/kg</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>SOUTH AFRICA</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-navel-oranges-oranazakbctns1</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:47:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>South Africa Orange Naval Cambria</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>AED 8.95/kg</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-naval-cambria-1755379961-mdywnze-mdywnzffmtc1ntm3otk2mq.html</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:48:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Green Watermelon Long</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>AED 4.39</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/melon/watermelon-long-green/p/489894?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:49:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Watermelon Egypt 1.5 kg</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/373189-ea/?convtobuom=1500</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:49:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>AED 12.95/kg</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:49:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Watermelon Kernel</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>AED 65.00/kg</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>NATURE'S CHOICE</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/pantry/nuts-seeds-dried-fruits/natures-choice-watermelon-kernel-fxswaaenc100l1</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:50:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/water-melon-1756071158-mde3mja-mde3mjbfmtc1nja3mte1oa.html</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:50:16</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H397"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16890,6 +16890,1686 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>AED 9.69</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/garlic-ginger/garlic-kg-ep/p/499952?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>2026-07-11 14:02:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>AED 5.39</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/cucumber/cucumber-kg-ep/p/449729?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:55:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Sweet Potato (Orange)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>AED 9.99</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/potato/potato-sweet-import/p/458471?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:57:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>AED 3.79</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/onion-shalots/onion-red-ep/p/447550?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Premium Tomato Bunch</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>AED 7.99</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/tomato/tomato-bunch-red-premium-ph/p/1792194?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:01:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Carrefour Valencia Oranges 3Kg</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>AED 4.33</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/crf-orange-valencia-3kg/p/2175463?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>AED 8.89</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/orange/orange-navel/p/71069?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:08:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Green Watermelon Long</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>AED 4.39</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>carrefour</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://www.carrefouruae.com/mafuae/en/melon/watermelon-long-green/p/489894?offer=offer_carrefour_&amp;sid=SLOTTED&amp;sellerId=0000</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:12:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:58:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Cucumber 500 g</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>AED 5.96/kg</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/p/18574-ea/?convtobuom=500</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:55:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:55:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Snack Cucumbers</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>AED 14.00/kg</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/cucumbers/veggitech-snack-cucumbers-cucmiaexx2xxl1</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:55:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>cucumber</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Cucumber</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Loose Cucumber</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/cucumber-loose-uae-463632.html</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:56:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Shan Ginger Garlic Paste 310 g</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>AED 30.81/kg</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/shan-ginger-garlic-paste-310-g/p/652365/?</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>2026-07-11 14:03:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:57:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Purple Garlic</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>AED 86.76/kg</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>SPAIN</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/garlic-ginger/kibsons-purple-garlic-garpuesxx30ps1</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:57:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Loose Garlic</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>AED 9.75/kg</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/garlic-loose-china-462760.html</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:57:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Potato 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>AED 4.50/kg</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/potato-2-5-kg/p/991526/?</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:58:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Sweet Potatoes</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>AED 21.95/kg</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>UNITED STATES</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/potatoes/kibsons-sweet-potatoes-potxxusxxkgsa1</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:58:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Potato Syria</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>AED 4.24/kg</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/potato-1700602554-mdawmdawmtm4mziwmq-mdawmdawmtm4mziwmv8xnzawnjayntu0.html</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:59:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Red Onion Sliced 250 g</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>AED 16.00/kg</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/red-onion-sliced-250-g/p/893372/?</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:00:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Red Onions</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>AED 6.40/kg</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/onions/kibsons-red-onions-onireinxxkgss1</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:00:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>red_onion</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Red Onion</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Vegan Organic Red Onion</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>AED 42.00/kg</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/red-onion-organic-1701293480-mdawmdawmtm4ndgyng-mdawmdawmtm4ndgynl8xnzaxmjkzndgw.html</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:01:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>LuLu Whole Peeled Tomatoes in Tomato Juice 400 g</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>AED 14.12/kg</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/lulu-whole-peeled-tomatoes-in-tomato-juice-400-g/p/879023/?</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:01:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:02:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>AED 5.50/kg</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/tomato-per-kg-4409651.html</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:02:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Tomato</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Cherry Tomatoes</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>AED 28.33/kg</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/vegetables/tomatoes/veggitech-cherry-tomatoes-tomcraexxxxxl1</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:06:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Orange Valencia 2.5 kg</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>AED 5.98/kg</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/orange-valencia-2-5-kg/p/736734/?</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:06:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Valencia Oranges</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>AED 15.00/kg</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>LEBANON</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/fruits/citrus/kibsons-valencia-oranges-oravalbxxpacb1</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:07:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>orange_valencia</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Orange Valencia</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Orange Organic</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>AED 51.90/kg</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-organic-1695423680-odk1njiznzc4otu2nq-odk1njiznzc4otu2nv8xnjk1ndiznjgw.html</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Organic Navel Orange 1 pkt</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>AED 9.56/L</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/organic-navel-orange-1-pkt/p/1335864/?</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:08:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:09:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>South Africa Orange Naval Cambria</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>AED 8.95/kg</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/orange-naval-cambria-1755379961-mdywnze-mdywnzffmtc1ntm3otk2mq.html</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:09:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>orange_navel</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Orange Navel</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Orange Marmalade</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>AED 42.06/kg</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>SAINSBURY'S</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/sainsburys-/honey-jams-spreads/sainsburys-orange-marmalade-mambouksb340s1</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Watermelon Saudi 2 kg</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>AED 4.45/kg</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>lulu</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://gcc.luluhypermarket.com/en-ae/watermelon-saudi-2-kg/p/2262476-ea/?convtobuom=2000</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Fruits</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>AED 85.68/kg</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>barakat</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://barakatfresh.ae/fruits.html</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:12:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Watermelon Kernel</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>AED 65.00/kg</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>NATURE'S CHOICE</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>kibsons</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://www.kibsons.com/en/product/pantry/nuts-seeds-dried-fruits/natures-choice-watermelon-kernel-fxswaaenc100l1</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:13:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>watermelon</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Watermelon</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>AED 4.95/kg</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>unioncoop</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://www.unioncoop.ae/water-melon-1756071158-mde3mja-mde3mjbfmtc1nja3mte1oa.html</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>2026-07-11 13:13:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
